--- a/backend/data/financials_by_company/1903.HK.xlsx
+++ b/backend/data/financials_by_company/1903.HK.xlsx
@@ -3774,10 +3774,8 @@
           <t>Johor Bahru</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>81200</t>
-        </is>
+      <c r="D2" t="n">
+        <v>81200</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3994,7 +3992,7 @@
         <v>-133000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>2.687</v>
@@ -4198,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>-0.1336</v>
